--- a/Reference/Merge Table UI.xlsx
+++ b/Reference/Merge Table UI.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XenAnalyticTransl\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E6E35304-0705-4E64-9DEB-2DE9D6B2010E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A33E8F0-619E-490D-9DBE-9460DA7FCFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="5" r:id="rId2"/>
-    <sheet name="arrow atas" sheetId="4" r:id="rId3"/>
-    <sheet name="arrow bawah" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
+    <sheet name="Sheet1 (2)" sheetId="5" state="hidden" r:id="rId2"/>
+    <sheet name="merge 1-3" sheetId="8" r:id="rId3"/>
+    <sheet name="top arrow" sheetId="4" r:id="rId4"/>
+    <sheet name="mid arrow 1" sheetId="6" r:id="rId5"/>
+    <sheet name="mid arrow 2" sheetId="7" r:id="rId6"/>
+    <sheet name="bottom arrow" sheetId="2" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="100">
   <si>
     <t>ProfileId</t>
   </si>
@@ -261,6 +264,84 @@
   </si>
   <si>
     <t>When Trip Signal is On, turn on Trip Alarm, turn on Trip Buzzer once.    When HMI Acknowledge, turn off Trip Buzzer.</t>
+  </si>
+  <si>
+    <t>StatementPropertyPlcVariable</t>
+  </si>
+  <si>
+    <t>StatementPropertyPlcValue</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
 </sst>
 </file>
@@ -284,7 +365,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -309,6 +390,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -322,11 +409,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,11 +885,11 @@
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <f>_xlfn.XLOOKUP(J2,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" ref="K2:K23" si="0">_xlfn.XLOOKUP(J2,$U$2:$U$17,$V$2:$V$17,"")</f>
         <v>Operation Mode</v>
       </c>
       <c r="L2" t="str">
-        <f>_xlfn.XLOOKUP(J2,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" ref="L2:L23" si="1">_xlfn.XLOOKUP(J2,$U$2:$U$17,$Y$2:$Y$17,"")</f>
         <v>blnMA</v>
       </c>
       <c r="M2">
@@ -890,19 +979,19 @@
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <f>_xlfn.XLOOKUP(J3,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Mode</v>
       </c>
       <c r="L3" t="str">
-        <f>_xlfn.XLOOKUP(J3,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMA</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M23" si="0">_xlfn.XLOOKUP(K3,$V$2:$V$17,$W$2:$W$17,"")</f>
+        <f t="shared" ref="M3:M23" si="2">_xlfn.XLOOKUP(K3,$V$2:$V$17,$W$2:$W$17,"")</f>
         <v>1</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N23" si="1">_xlfn.XLOOKUP(M3,$W$2:$W$17,$X$2:$X$17,"")</f>
+        <f t="shared" ref="N3:N23" si="3">_xlfn.XLOOKUP(M3,$W$2:$W$17,$X$2:$X$17,"")</f>
         <v>HMI</v>
       </c>
       <c r="O3" t="s">
@@ -924,7 +1013,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X17" si="2">_xlfn.XLOOKUP(W3,$AB$2:$AB$5,$AC$2:$AC$5,"")</f>
+        <f t="shared" ref="X3:X17" si="4">_xlfn.XLOOKUP(W3,$AB$2:$AB$5,$AC$2:$AC$5,"")</f>
         <v>HMI</v>
       </c>
       <c r="Y3" t="s">
@@ -984,19 +1073,19 @@
         <v>2</v>
       </c>
       <c r="K4" t="str">
-        <f>_xlfn.XLOOKUP(J4,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>MCC Trip</v>
       </c>
       <c r="L4" t="str">
-        <f>_xlfn.XLOOKUP(J4,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O4" t="s">
@@ -1018,7 +1107,7 @@
         <v>1</v>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y4" t="s">
@@ -1069,19 +1158,19 @@
         <v>2</v>
       </c>
       <c r="K5" t="str">
-        <f>_xlfn.XLOOKUP(J5,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>MCC Trip</v>
       </c>
       <c r="L5" t="str">
-        <f>_xlfn.XLOOKUP(J5,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O5" t="s">
@@ -1103,7 +1192,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y5" t="s">
@@ -1154,19 +1243,19 @@
         <v>4</v>
       </c>
       <c r="K6" t="str">
-        <f>_xlfn.XLOOKUP(J6,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Manual</v>
       </c>
       <c r="L6" t="str">
-        <f>_xlfn.XLOOKUP(J6,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMC</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O6" t="s">
@@ -1188,7 +1277,7 @@
         <v>2</v>
       </c>
       <c r="X6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y6" t="s">
@@ -1230,19 +1319,19 @@
         <v>4</v>
       </c>
       <c r="K7" t="str">
-        <f>_xlfn.XLOOKUP(J7,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Manual</v>
       </c>
       <c r="L7" t="str">
-        <f>_xlfn.XLOOKUP(J7,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMC</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O7" t="s">
@@ -1264,7 +1353,7 @@
         <v>2</v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y7" t="s">
@@ -1306,19 +1395,19 @@
         <v>5</v>
       </c>
       <c r="K8" t="str">
-        <f>_xlfn.XLOOKUP(J8,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Signal</v>
       </c>
       <c r="L8" t="str">
-        <f>_xlfn.XLOOKUP(J8,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnTRP</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O8" t="s">
@@ -1340,7 +1429,7 @@
         <v>2</v>
       </c>
       <c r="X8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y8" t="s">
@@ -1382,19 +1471,19 @@
         <v>5</v>
       </c>
       <c r="K9" t="str">
-        <f>_xlfn.XLOOKUP(J9,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Signal</v>
       </c>
       <c r="L9" t="str">
-        <f>_xlfn.XLOOKUP(J9,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnTRP</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O9" t="s">
@@ -1416,7 +1505,7 @@
         <v>2</v>
       </c>
       <c r="X9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y9" t="s">
@@ -1458,19 +1547,19 @@
         <v>6</v>
       </c>
       <c r="K10" t="str">
-        <f>_xlfn.XLOOKUP(J10,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Signal</v>
       </c>
       <c r="L10" t="str">
-        <f>_xlfn.XLOOKUP(J10,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnRUN</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O10" t="s">
@@ -1492,7 +1581,7 @@
         <v>3</v>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Delay Timer</v>
       </c>
       <c r="Y10" t="s">
@@ -1519,19 +1608,19 @@
         <v>6</v>
       </c>
       <c r="K11" t="str">
-        <f>_xlfn.XLOOKUP(J11,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Signal</v>
       </c>
       <c r="L11" t="str">
-        <f>_xlfn.XLOOKUP(J11,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnRUN</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O11" t="s">
@@ -1553,7 +1642,7 @@
         <v>4</v>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Time Recorder</v>
       </c>
       <c r="Y11" t="s">
@@ -1580,19 +1669,19 @@
         <v>7</v>
       </c>
       <c r="K12" t="str">
-        <f>_xlfn.XLOOKUP(J12,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Command</v>
       </c>
       <c r="L12" t="str">
-        <f>_xlfn.XLOOKUP(J12,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnOut</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O12" t="s">
@@ -1614,7 +1703,7 @@
         <v>1</v>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y12" t="s">
@@ -1641,19 +1730,19 @@
         <v>7</v>
       </c>
       <c r="K13" t="str">
-        <f>_xlfn.XLOOKUP(J13,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Command</v>
       </c>
       <c r="L13" t="str">
-        <f>_xlfn.XLOOKUP(J13,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnOut</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O13" t="s">
@@ -1675,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y13" t="s">
@@ -1702,19 +1791,19 @@
         <v>12</v>
       </c>
       <c r="K14" t="str">
-        <f>_xlfn.XLOOKUP(J14,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Alarm</v>
       </c>
       <c r="L14" t="str">
-        <f>_xlfn.XLOOKUP(J14,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O14" t="s">
@@ -1736,7 +1825,7 @@
         <v>1</v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y14" t="s">
@@ -1763,19 +1852,19 @@
         <v>12</v>
       </c>
       <c r="K15" t="str">
-        <f>_xlfn.XLOOKUP(J15,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Alarm</v>
       </c>
       <c r="L15" t="str">
-        <f>_xlfn.XLOOKUP(J15,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O15" t="s">
@@ -1797,7 +1886,7 @@
         <v>1</v>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y15" t="s">
@@ -1824,19 +1913,19 @@
         <v>13</v>
       </c>
       <c r="K16" t="str">
-        <f>_xlfn.XLOOKUP(J16,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Alarm</v>
       </c>
       <c r="L16" t="str">
-        <f>_xlfn.XLOOKUP(J16,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O16" t="s">
@@ -1858,7 +1947,7 @@
         <v>1</v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y16" t="s">
@@ -1885,19 +1974,19 @@
         <v>13</v>
       </c>
       <c r="K17" t="str">
-        <f>_xlfn.XLOOKUP(J17,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Alarm</v>
       </c>
       <c r="L17" t="str">
-        <f>_xlfn.XLOOKUP(J17,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O17" t="s">
@@ -1919,7 +2008,7 @@
         <v>1</v>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y17" t="s">
@@ -1946,19 +2035,19 @@
         <v>14</v>
       </c>
       <c r="K18" t="str">
-        <f>_xlfn.XLOOKUP(J18,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Sequence Auto</v>
       </c>
       <c r="L18" t="str">
-        <f>_xlfn.XLOOKUP(J18,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnAUT</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O18" t="s">
@@ -1988,19 +2077,19 @@
         <v>14</v>
       </c>
       <c r="K19" t="str">
-        <f>_xlfn.XLOOKUP(J19,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Sequence Auto</v>
       </c>
       <c r="L19" t="str">
-        <f>_xlfn.XLOOKUP(J19,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnAUT</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O19" t="s">
@@ -2030,19 +2119,19 @@
         <v>15</v>
       </c>
       <c r="K20" t="str">
-        <f>_xlfn.XLOOKUP(J20,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Buzzer</v>
       </c>
       <c r="L20" t="str">
-        <f>_xlfn.XLOOKUP(J20,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O20" t="s">
@@ -2072,19 +2161,19 @@
         <v>15</v>
       </c>
       <c r="K21" t="str">
-        <f>_xlfn.XLOOKUP(J21,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Buzzer</v>
       </c>
       <c r="L21" t="str">
-        <f>_xlfn.XLOOKUP(J21,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O21" t="s">
@@ -2114,19 +2203,19 @@
         <v>16</v>
       </c>
       <c r="K22" t="str">
-        <f>_xlfn.XLOOKUP(J22,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Buzzer</v>
       </c>
       <c r="L22" t="str">
-        <f>_xlfn.XLOOKUP(J22,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O22" t="s">
@@ -2156,19 +2245,19 @@
         <v>16</v>
       </c>
       <c r="K23" t="str">
-        <f>_xlfn.XLOOKUP(J23,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Buzzer</v>
       </c>
       <c r="L23" t="str">
-        <f>_xlfn.XLOOKUP(J23,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O23" t="s">
@@ -2287,25 +2376,25 @@
       <c r="J1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="Q1" s="2" t="s">
         <v>0</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -2389,11 +2478,11 @@
         <v>1</v>
       </c>
       <c r="K2" t="str">
-        <f>_xlfn.XLOOKUP(J2,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" ref="K2:K23" si="0">_xlfn.XLOOKUP(J2,$U$2:$U$17,$V$2:$V$17,"")</f>
         <v>Operation Mode</v>
       </c>
       <c r="L2" t="str">
-        <f>_xlfn.XLOOKUP(J2,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" ref="L2:L23" si="1">_xlfn.XLOOKUP(J2,$U$2:$U$17,$Y$2:$Y$17,"")</f>
         <v>blnMA</v>
       </c>
       <c r="M2">
@@ -2495,19 +2584,19 @@
         <v>1</v>
       </c>
       <c r="K3" t="str">
-        <f>_xlfn.XLOOKUP(J3,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Mode</v>
       </c>
       <c r="L3" t="str">
-        <f>_xlfn.XLOOKUP(J3,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMA</v>
       </c>
       <c r="M3">
-        <f t="shared" ref="M3:M23" si="0">_xlfn.XLOOKUP(K3,$V$2:$V$17,$W$2:$W$17,"")</f>
+        <f t="shared" ref="M3:M23" si="2">_xlfn.XLOOKUP(K3,$V$2:$V$17,$W$2:$W$17,"")</f>
         <v>1</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N23" si="1">_xlfn.XLOOKUP(M3,$W$2:$W$17,$X$2:$X$17,"")</f>
+        <f t="shared" ref="N3:N23" si="3">_xlfn.XLOOKUP(M3,$W$2:$W$17,$X$2:$X$17,"")</f>
         <v>HMI</v>
       </c>
       <c r="O3" t="s">
@@ -2529,7 +2618,7 @@
         <v>1</v>
       </c>
       <c r="X3" t="str">
-        <f t="shared" ref="X3:X17" si="2">_xlfn.XLOOKUP(W3,$AB$2:$AB$5,$AC$2:$AC$5,"")</f>
+        <f t="shared" ref="X3:X17" si="4">_xlfn.XLOOKUP(W3,$AB$2:$AB$5,$AC$2:$AC$5,"")</f>
         <v>HMI</v>
       </c>
       <c r="Y3" t="s">
@@ -2601,19 +2690,19 @@
         <v>2</v>
       </c>
       <c r="K4" t="str">
-        <f>_xlfn.XLOOKUP(J4,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>MCC Trip</v>
       </c>
       <c r="L4" t="str">
-        <f>_xlfn.XLOOKUP(J4,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M4">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N4" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O4" t="s">
@@ -2635,7 +2724,7 @@
         <v>1</v>
       </c>
       <c r="X4" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y4" t="s">
@@ -2698,19 +2787,19 @@
         <v>2</v>
       </c>
       <c r="K5" t="str">
-        <f>_xlfn.XLOOKUP(J5,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>MCC Trip</v>
       </c>
       <c r="L5" t="str">
-        <f>_xlfn.XLOOKUP(J5,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M5">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N5" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O5" t="s">
@@ -2732,7 +2821,7 @@
         <v>1</v>
       </c>
       <c r="X5" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y5" t="s">
@@ -2795,19 +2884,19 @@
         <v>4</v>
       </c>
       <c r="K6" t="str">
-        <f>_xlfn.XLOOKUP(J6,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Manual</v>
       </c>
       <c r="L6" t="str">
-        <f>_xlfn.XLOOKUP(J6,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMC</v>
       </c>
       <c r="M6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N6" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O6" t="s">
@@ -2829,7 +2918,7 @@
         <v>2</v>
       </c>
       <c r="X6" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y6" t="s">
@@ -2883,19 +2972,19 @@
         <v>4</v>
       </c>
       <c r="K7" t="str">
-        <f>_xlfn.XLOOKUP(J7,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Manual</v>
       </c>
       <c r="L7" t="str">
-        <f>_xlfn.XLOOKUP(J7,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnMC</v>
       </c>
       <c r="M7">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N7" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O7" t="s">
@@ -2917,7 +3006,7 @@
         <v>2</v>
       </c>
       <c r="X7" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y7" t="s">
@@ -2971,19 +3060,19 @@
         <v>5</v>
       </c>
       <c r="K8" t="str">
-        <f>_xlfn.XLOOKUP(J8,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Signal</v>
       </c>
       <c r="L8" t="str">
-        <f>_xlfn.XLOOKUP(J8,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnTRP</v>
       </c>
       <c r="M8">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N8" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O8" t="s">
@@ -3005,7 +3094,7 @@
         <v>2</v>
       </c>
       <c r="X8" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y8" t="s">
@@ -3059,19 +3148,19 @@
         <v>5</v>
       </c>
       <c r="K9" t="str">
-        <f>_xlfn.XLOOKUP(J9,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Signal</v>
       </c>
       <c r="L9" t="str">
-        <f>_xlfn.XLOOKUP(J9,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnTRP</v>
       </c>
       <c r="M9">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N9" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O9" t="s">
@@ -3093,7 +3182,7 @@
         <v>2</v>
       </c>
       <c r="X9" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>PLC</v>
       </c>
       <c r="Y9" t="s">
@@ -3147,19 +3236,19 @@
         <v>6</v>
       </c>
       <c r="K10" t="str">
-        <f>_xlfn.XLOOKUP(J10,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Signal</v>
       </c>
       <c r="L10" t="str">
-        <f>_xlfn.XLOOKUP(J10,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnRUN</v>
       </c>
       <c r="M10">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N10" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O10" t="s">
@@ -3181,7 +3270,7 @@
         <v>3</v>
       </c>
       <c r="X10" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Delay Timer</v>
       </c>
       <c r="Y10" t="s">
@@ -3220,19 +3309,19 @@
         <v>6</v>
       </c>
       <c r="K11" t="str">
-        <f>_xlfn.XLOOKUP(J11,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Operation Signal</v>
       </c>
       <c r="L11" t="str">
-        <f>_xlfn.XLOOKUP(J11,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnRUN</v>
       </c>
       <c r="M11">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N11" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O11" t="s">
@@ -3254,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="X11" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Time Recorder</v>
       </c>
       <c r="Y11" t="s">
@@ -3281,19 +3370,19 @@
         <v>7</v>
       </c>
       <c r="K12" t="str">
-        <f>_xlfn.XLOOKUP(J12,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Command</v>
       </c>
       <c r="L12" t="str">
-        <f>_xlfn.XLOOKUP(J12,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnOut</v>
       </c>
       <c r="M12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N12" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O12" t="s">
@@ -3315,7 +3404,7 @@
         <v>1</v>
       </c>
       <c r="X12" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y12" t="s">
@@ -3342,19 +3431,19 @@
         <v>7</v>
       </c>
       <c r="K13" t="str">
-        <f>_xlfn.XLOOKUP(J13,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Command</v>
       </c>
       <c r="L13" t="str">
-        <f>_xlfn.XLOOKUP(J13,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnOut</v>
       </c>
       <c r="M13">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>2</v>
       </c>
       <c r="N13" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>PLC</v>
       </c>
       <c r="O13" t="s">
@@ -3376,7 +3465,7 @@
         <v>1</v>
       </c>
       <c r="X13" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y13" t="s">
@@ -3403,19 +3492,19 @@
         <v>12</v>
       </c>
       <c r="K14" t="str">
-        <f>_xlfn.XLOOKUP(J14,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Alarm</v>
       </c>
       <c r="L14" t="str">
-        <f>_xlfn.XLOOKUP(J14,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M14">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N14" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O14" t="s">
@@ -3437,7 +3526,7 @@
         <v>1</v>
       </c>
       <c r="X14" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y14" t="s">
@@ -3464,19 +3553,19 @@
         <v>12</v>
       </c>
       <c r="K15" t="str">
-        <f>_xlfn.XLOOKUP(J15,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Alarm</v>
       </c>
       <c r="L15" t="str">
-        <f>_xlfn.XLOOKUP(J15,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M15">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N15" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O15" t="s">
@@ -3498,7 +3587,7 @@
         <v>1</v>
       </c>
       <c r="X15" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y15" t="s">
@@ -3525,19 +3614,19 @@
         <v>13</v>
       </c>
       <c r="K16" t="str">
-        <f>_xlfn.XLOOKUP(J16,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Alarm</v>
       </c>
       <c r="L16" t="str">
-        <f>_xlfn.XLOOKUP(J16,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M16">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N16" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O16" t="s">
@@ -3559,7 +3648,7 @@
         <v>1</v>
       </c>
       <c r="X16" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y16" t="s">
@@ -3586,19 +3675,19 @@
         <v>13</v>
       </c>
       <c r="K17" t="str">
-        <f>_xlfn.XLOOKUP(J17,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Alarm</v>
       </c>
       <c r="L17" t="str">
-        <f>_xlfn.XLOOKUP(J17,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M17">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N17" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O17" t="s">
@@ -3620,7 +3709,7 @@
         <v>1</v>
       </c>
       <c r="X17" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>HMI</v>
       </c>
       <c r="Y17" t="s">
@@ -3647,19 +3736,19 @@
         <v>14</v>
       </c>
       <c r="K18" t="str">
-        <f>_xlfn.XLOOKUP(J18,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Sequence Auto</v>
       </c>
       <c r="L18" t="str">
-        <f>_xlfn.XLOOKUP(J18,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnAUT</v>
       </c>
       <c r="M18">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N18" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O18" t="s">
@@ -3689,19 +3778,19 @@
         <v>14</v>
       </c>
       <c r="K19" t="str">
-        <f>_xlfn.XLOOKUP(J19,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Sequence Auto</v>
       </c>
       <c r="L19" t="str">
-        <f>_xlfn.XLOOKUP(J19,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>blnAUT</v>
       </c>
       <c r="M19">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N19" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O19" t="s">
@@ -3731,19 +3820,19 @@
         <v>15</v>
       </c>
       <c r="K20" t="str">
-        <f>_xlfn.XLOOKUP(J20,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Buzzer</v>
       </c>
       <c r="L20" t="str">
-        <f>_xlfn.XLOOKUP(J20,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M20">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N20" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O20" t="s">
@@ -3773,19 +3862,19 @@
         <v>15</v>
       </c>
       <c r="K21" t="str">
-        <f>_xlfn.XLOOKUP(J21,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Run Fail Buzzer</v>
       </c>
       <c r="L21" t="str">
-        <f>_xlfn.XLOOKUP(J21,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O21" t="s">
@@ -3815,19 +3904,19 @@
         <v>16</v>
       </c>
       <c r="K22" t="str">
-        <f>_xlfn.XLOOKUP(J22,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Buzzer</v>
       </c>
       <c r="L22" t="str">
-        <f>_xlfn.XLOOKUP(J22,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N22" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O22" t="s">
@@ -3857,19 +3946,19 @@
         <v>16</v>
       </c>
       <c r="K23" t="str">
-        <f>_xlfn.XLOOKUP(J23,$U$2:$U$17,$V$2:$V$17,"")</f>
+        <f t="shared" si="0"/>
         <v>Trip Buzzer</v>
       </c>
       <c r="L23" t="str">
-        <f>_xlfn.XLOOKUP(J23,$U$2:$U$17,$Y$2:$Y$17,"")</f>
+        <f t="shared" si="1"/>
         <v>New Instance</v>
       </c>
       <c r="M23">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="N23" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>HMI</v>
       </c>
       <c r="O23" t="s">
@@ -3938,20 +4027,21 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8976131B-78D4-4767-A06A-241F09171867}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7814A5A0-8059-423C-AF21-3E392F93D4CF}">
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.26953125" customWidth="1"/>
-    <col min="9" max="9" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.90625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.35">
@@ -3968,795 +4058,795 @@
         <v>52</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="G1" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="I1" s="3" t="s">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C2" t="s">
+        <v>76</v>
       </c>
       <c r="D2" t="s">
         <v>50</v>
       </c>
-      <c r="E2">
-        <v>1</v>
+      <c r="E2" t="s">
+        <v>76</v>
       </c>
       <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" t="s">
         <v>44</v>
       </c>
-      <c r="G2" t="s">
+      <c r="I2" t="s">
         <v>19</v>
       </c>
-      <c r="H2">
-        <v>0</v>
-      </c>
-      <c r="I2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
+      <c r="J2" t="s">
+        <v>77</v>
       </c>
       <c r="K2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3" t="s">
+        <v>76</v>
+      </c>
+      <c r="F3" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="G3" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" t="s">
         <v>44</v>
       </c>
-      <c r="G3" t="s">
+      <c r="I3" t="s">
         <v>19</v>
       </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3" t="s">
+      <c r="J3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" t="s">
         <v>3</v>
       </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3" t="s">
-        <v>18</v>
-      </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4">
+      <c r="A4" t="s">
+        <v>79</v>
+      </c>
+      <c r="B4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>77</v>
+      </c>
+      <c r="K4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>80</v>
+      </c>
+      <c r="B5" t="s">
+        <v>76</v>
+      </c>
+      <c r="C5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5" t="s">
+        <v>78</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" t="s">
+        <v>44</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>77</v>
+      </c>
+      <c r="K5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B6" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" t="s">
+        <v>76</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>80</v>
+      </c>
+      <c r="F6" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G6" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" t="s">
         <v>44</v>
       </c>
-      <c r="G4" t="s">
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>77</v>
+      </c>
+      <c r="K7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>83</v>
+      </c>
+      <c r="B8" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>78</v>
+      </c>
+      <c r="H8" t="s">
+        <v>45</v>
+      </c>
+      <c r="I8" t="s">
+        <v>25</v>
+      </c>
+      <c r="J8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>84</v>
+      </c>
+      <c r="B9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9" t="s">
+        <v>81</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>78</v>
+      </c>
+      <c r="H9" t="s">
+        <v>45</v>
+      </c>
+      <c r="I9" t="s">
+        <v>25</v>
+      </c>
+      <c r="J9" t="s">
+        <v>77</v>
+      </c>
+      <c r="K9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" t="s">
+        <v>82</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10" t="s">
+        <v>78</v>
+      </c>
+      <c r="H10" t="s">
+        <v>45</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C11" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11" t="s">
+        <v>77</v>
+      </c>
+      <c r="K11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" t="s">
+        <v>76</v>
+      </c>
+      <c r="C12" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12" t="s">
+        <v>83</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" t="s">
+        <v>78</v>
+      </c>
+      <c r="H12" t="s">
+        <v>45</v>
+      </c>
+      <c r="I12" t="s">
+        <v>29</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" t="s">
+        <v>76</v>
+      </c>
+      <c r="C13" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
+        <v>83</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" t="s">
+        <v>78</v>
+      </c>
+      <c r="H13" t="s">
+        <v>45</v>
+      </c>
+      <c r="I13" t="s">
+        <v>29</v>
+      </c>
+      <c r="J13" t="s">
+        <v>77</v>
+      </c>
+      <c r="K13" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
+        <v>87</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" t="s">
+        <v>44</v>
+      </c>
+      <c r="I14" t="s">
         <v>21</v>
       </c>
-      <c r="H4">
-        <v>0</v>
-      </c>
-      <c r="I4" t="s">
-        <v>4</v>
-      </c>
-      <c r="J4">
-        <v>2</v>
-      </c>
-      <c r="K4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
-        <v>50</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5" t="s">
+      <c r="J14" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>90</v>
+      </c>
+      <c r="B15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" t="s">
+        <v>76</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15" t="s">
+        <v>87</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" t="s">
         <v>44</v>
       </c>
-      <c r="G5" t="s">
+      <c r="I15" t="s">
         <v>21</v>
       </c>
-      <c r="H5">
-        <v>0</v>
-      </c>
-      <c r="I5" t="s">
-        <v>5</v>
-      </c>
-      <c r="J5">
-        <v>2</v>
-      </c>
-      <c r="K5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="J15" t="s">
+        <v>77</v>
+      </c>
+      <c r="K15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B16" t="s">
+        <v>76</v>
+      </c>
+      <c r="C16" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16" t="s">
+        <v>88</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" t="s">
         <v>44</v>
       </c>
-      <c r="G6" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6">
-        <v>4</v>
-      </c>
-      <c r="K6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="I16" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B17" t="s">
+        <v>76</v>
+      </c>
+      <c r="C17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" t="s">
+        <v>88</v>
+      </c>
+      <c r="F17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" t="s">
         <v>44</v>
       </c>
-      <c r="G7" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7">
-        <v>0</v>
-      </c>
-      <c r="I7" t="s">
-        <v>7</v>
-      </c>
-      <c r="J7">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>45</v>
-      </c>
-      <c r="G8" t="s">
-        <v>25</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>77</v>
+      </c>
+      <c r="K17" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>93</v>
+      </c>
+      <c r="B18" t="s">
+        <v>76</v>
+      </c>
+      <c r="C18" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18" t="s">
+        <v>94</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" t="s">
+        <v>44</v>
+      </c>
+      <c r="I18" t="s">
+        <v>39</v>
+      </c>
+      <c r="J18" t="s">
+        <v>76</v>
+      </c>
+      <c r="K18" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" t="s">
+        <v>76</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" t="s">
+        <v>94</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I19" t="s">
+        <v>39</v>
+      </c>
+      <c r="J19" t="s">
+        <v>77</v>
+      </c>
+      <c r="K19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>96</v>
+      </c>
+      <c r="B20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" t="s">
+        <v>44</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" t="s">
         <v>8</v>
       </c>
-      <c r="J8">
-        <v>5</v>
-      </c>
-      <c r="K8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A9">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>97</v>
+      </c>
+      <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
+        <v>76</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" t="s">
+        <v>89</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" t="s">
+        <v>44</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>77</v>
+      </c>
+      <c r="K21" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>98</v>
+      </c>
+      <c r="B22" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" t="s">
+        <v>90</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" t="s">
+        <v>21</v>
+      </c>
+      <c r="J22" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>1</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
-        <v>50</v>
-      </c>
-      <c r="E9">
-        <v>2</v>
-      </c>
-      <c r="F9" t="s">
-        <v>45</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9" t="s">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>99</v>
+      </c>
+      <c r="B23" t="s">
+        <v>76</v>
+      </c>
+      <c r="C23" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>77</v>
+      </c>
+      <c r="K23" t="s">
         <v>9</v>
-      </c>
-      <c r="J9">
-        <v>5</v>
-      </c>
-      <c r="K9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A10">
-        <v>10</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10" t="s">
-        <v>50</v>
-      </c>
-      <c r="E10">
-        <v>2</v>
-      </c>
-      <c r="F10" t="s">
-        <v>45</v>
-      </c>
-      <c r="G10" t="s">
-        <v>27</v>
-      </c>
-      <c r="H10">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>10</v>
-      </c>
-      <c r="J10">
-        <v>6</v>
-      </c>
-      <c r="K10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A11">
-        <v>11</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="F11" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" t="s">
-        <v>27</v>
-      </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11" t="s">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>6</v>
-      </c>
-      <c r="K11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12">
-        <v>12</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>45</v>
-      </c>
-      <c r="G12" t="s">
-        <v>29</v>
-      </c>
-      <c r="H12">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>10</v>
-      </c>
-      <c r="J12">
-        <v>7</v>
-      </c>
-      <c r="K12" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13">
-        <v>13</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G13" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13">
-        <v>0</v>
-      </c>
-      <c r="I13" t="s">
-        <v>7</v>
-      </c>
-      <c r="J13">
-        <v>7</v>
-      </c>
-      <c r="K13" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <v>1</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14" t="s">
-        <v>50</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="F14" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" t="s">
-        <v>21</v>
-      </c>
-      <c r="H14">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>8</v>
-      </c>
-      <c r="J14">
-        <v>12</v>
-      </c>
-      <c r="K14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15">
-        <v>16</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
-      </c>
-      <c r="F15" t="s">
-        <v>44</v>
-      </c>
-      <c r="G15" t="s">
-        <v>21</v>
-      </c>
-      <c r="H15">
-        <v>0</v>
-      </c>
-      <c r="I15" t="s">
-        <v>9</v>
-      </c>
-      <c r="J15">
-        <v>12</v>
-      </c>
-      <c r="K15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16">
-        <v>17</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-      <c r="F16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" t="s">
-        <v>21</v>
-      </c>
-      <c r="H16">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>8</v>
-      </c>
-      <c r="J16">
-        <v>13</v>
-      </c>
-      <c r="K16" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A17">
-        <v>18</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-      <c r="F17" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" t="s">
-        <v>21</v>
-      </c>
-      <c r="H17">
-        <v>0</v>
-      </c>
-      <c r="I17" t="s">
-        <v>9</v>
-      </c>
-      <c r="J17">
-        <v>13</v>
-      </c>
-      <c r="K17" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A18">
-        <v>19</v>
-      </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="F18" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>11</v>
-      </c>
-      <c r="J18">
-        <v>14</v>
-      </c>
-      <c r="K18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A19">
-        <v>20</v>
-      </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19" t="s">
-        <v>50</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-      <c r="F19" t="s">
-        <v>44</v>
-      </c>
-      <c r="G19" t="s">
-        <v>39</v>
-      </c>
-      <c r="H19">
-        <v>0</v>
-      </c>
-      <c r="I19" t="s">
-        <v>12</v>
-      </c>
-      <c r="J19">
-        <v>14</v>
-      </c>
-      <c r="K19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A20">
-        <v>21</v>
-      </c>
-      <c r="B20">
-        <v>1</v>
-      </c>
-      <c r="C20">
-        <v>1</v>
-      </c>
-      <c r="D20" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-      <c r="F20" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" t="s">
-        <v>21</v>
-      </c>
-      <c r="H20">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>8</v>
-      </c>
-      <c r="J20">
-        <v>15</v>
-      </c>
-      <c r="K20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A21">
-        <v>22</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-      <c r="C21">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-      <c r="F21" t="s">
-        <v>44</v>
-      </c>
-      <c r="G21" t="s">
-        <v>21</v>
-      </c>
-      <c r="H21">
-        <v>0</v>
-      </c>
-      <c r="I21" t="s">
-        <v>9</v>
-      </c>
-      <c r="J21">
-        <v>15</v>
-      </c>
-      <c r="K21" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A22">
-        <v>23</v>
-      </c>
-      <c r="B22">
-        <v>1</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="F22" t="s">
-        <v>44</v>
-      </c>
-      <c r="G22" t="s">
-        <v>21</v>
-      </c>
-      <c r="H22">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22">
-        <v>16</v>
-      </c>
-      <c r="K22" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A23">
-        <v>24</v>
-      </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
-      </c>
-      <c r="F23" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" t="s">
-        <v>21</v>
-      </c>
-      <c r="H23">
-        <v>0</v>
-      </c>
-      <c r="I23" t="s">
-        <v>9</v>
-      </c>
-      <c r="J23">
-        <v>16</v>
-      </c>
-      <c r="K23" t="s">
-        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -4765,50 +4855,834 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50D9B80-349C-450A-9037-EC263D91D03C}">
-  <dimension ref="C1:F23"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8976131B-78D4-4767-A06A-241F09171867}">
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="17.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.6328125" customWidth="1"/>
+    <col min="10" max="10" width="21.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E1" t="s">
+      <c r="J1" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F2" t="s">
+        <v>19</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>2</v>
+      </c>
+      <c r="J4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>44</v>
+      </c>
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>4</v>
+      </c>
+      <c r="J6" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>44</v>
+      </c>
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+      <c r="J7" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>2</v>
+      </c>
+      <c r="E8" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" t="s">
+        <v>25</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+      <c r="J8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>2</v>
+      </c>
+      <c r="E9" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>5</v>
+      </c>
+      <c r="J9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>6</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>7</v>
+      </c>
+      <c r="J12" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>2</v>
+      </c>
+      <c r="E13" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>7</v>
+      </c>
+      <c r="J13" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14" t="s">
+        <v>44</v>
+      </c>
+      <c r="F14" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>12</v>
+      </c>
+      <c r="J14" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>44</v>
+      </c>
+      <c r="F15" t="s">
+        <v>21</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15">
+        <v>12</v>
+      </c>
+      <c r="J15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16" t="s">
+        <v>44</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>13</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>44</v>
+      </c>
+      <c r="F17" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <v>13</v>
+      </c>
+      <c r="J17" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
+      <c r="J18" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19" t="s">
+        <v>44</v>
+      </c>
+      <c r="F19" t="s">
+        <v>39</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>14</v>
+      </c>
+      <c r="J19" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F20" t="s">
+        <v>21</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20">
+        <v>15</v>
+      </c>
+      <c r="J20" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21" t="s">
+        <v>44</v>
+      </c>
+      <c r="F21" t="s">
+        <v>21</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>15</v>
+      </c>
+      <c r="J21" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" t="s">
+        <v>21</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>16</v>
+      </c>
+      <c r="J22" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>21</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23">
+        <v>16</v>
+      </c>
+      <c r="J23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58D0F3D6-8BBB-482B-A7E9-E6A981388C44}">
+  <dimension ref="A1:G23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.54296875" customWidth="1"/>
+    <col min="6" max="6" width="21.54296875" customWidth="1"/>
+    <col min="7" max="7" width="24.1796875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>18</v>
       </c>
       <c r="F2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>18</v>
@@ -4816,285 +5690,1439 @@
       <c r="F3">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C4" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
       </c>
       <c r="E4" t="s">
         <v>20</v>
       </c>
       <c r="F4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D5">
-        <v>2</v>
+        <v>2</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
       </c>
       <c r="E5" t="s">
         <v>20</v>
       </c>
       <c r="F5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C6" t="s">
-        <v>6</v>
-      </c>
-      <c r="D6">
-        <v>4</v>
+        <v>2</v>
+      </c>
+      <c r="G5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
       </c>
       <c r="E6" t="s">
         <v>3</v>
       </c>
       <c r="F6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7">
         <v>4</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C8" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>24</v>
       </c>
       <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D9">
         <v>5</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>24</v>
       </c>
       <c r="F9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C10" t="s">
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
         <v>10</v>
       </c>
-      <c r="D10">
-        <v>6</v>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
       </c>
       <c r="E10" t="s">
         <v>26</v>
       </c>
       <c r="F10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C11" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11">
         <v>6</v>
+      </c>
+      <c r="G10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>26</v>
       </c>
       <c r="F11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C12" t="s">
-        <v>10</v>
-      </c>
-      <c r="D12">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
       </c>
       <c r="E12" t="s">
         <v>28</v>
       </c>
       <c r="F12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C13" t="s">
         <v>7</v>
       </c>
-      <c r="D13">
-        <v>7</v>
+      <c r="G12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
       </c>
       <c r="E13" t="s">
         <v>28</v>
       </c>
       <c r="F13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C14" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14">
-        <v>12</v>
+        <v>7</v>
+      </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
       </c>
       <c r="E14" t="s">
         <v>36</v>
       </c>
       <c r="F14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C15" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15">
         <v>12</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
       </c>
       <c r="E15" t="s">
         <v>36</v>
       </c>
       <c r="F15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C16" t="s">
-        <v>8</v>
-      </c>
-      <c r="D16">
-        <v>13</v>
+        <v>12</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
       </c>
       <c r="E16" t="s">
         <v>37</v>
       </c>
       <c r="F16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C17" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17">
         <v>13</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
       </c>
       <c r="E17" t="s">
         <v>37</v>
       </c>
       <c r="F17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C18" t="s">
-        <v>11</v>
-      </c>
-      <c r="D18">
-        <v>14</v>
+        <v>13</v>
+      </c>
+      <c r="G17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
       </c>
       <c r="E18" t="s">
         <v>38</v>
       </c>
       <c r="F18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C19" t="s">
-        <v>12</v>
-      </c>
-      <c r="D19">
         <v>14</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
       </c>
       <c r="E19" t="s">
         <v>38</v>
       </c>
       <c r="F19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D20">
-        <v>15</v>
+        <v>14</v>
+      </c>
+      <c r="G19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
       </c>
       <c r="E20" t="s">
         <v>40</v>
       </c>
       <c r="F20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C21" t="s">
-        <v>9</v>
-      </c>
-      <c r="D21">
         <v>15</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
       </c>
       <c r="E21" t="s">
         <v>40</v>
       </c>
       <c r="F21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C22" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22">
-        <v>16</v>
+        <v>15</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
       </c>
       <c r="E22" t="s">
         <v>41</v>
       </c>
       <c r="F22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="3:6" x14ac:dyDescent="0.35">
-      <c r="C23" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23">
         <v>16</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
       </c>
       <c r="E23" t="s">
         <v>41</v>
       </c>
       <c r="F23">
-        <v>0</v>
+        <v>16</v>
+      </c>
+      <c r="G23">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5964435A-2873-4C04-A45F-0B9EB094C002}">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.54296875" customWidth="1"/>
+    <col min="6" max="6" width="26.54296875" customWidth="1"/>
+    <col min="7" max="7" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.1796875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="27.36328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4">
+        <v>2</v>
+      </c>
+      <c r="F4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5" t="s">
+        <v>50</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+      <c r="F5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="s">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6">
+        <v>4</v>
+      </c>
+      <c r="F6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>3</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7">
+        <v>0</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>50</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8" t="s">
+        <v>8</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>50</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9" t="s">
+        <v>9</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>10</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+      <c r="H10" t="s">
+        <v>10</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>11</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11">
+        <v>6</v>
+      </c>
+      <c r="F11" t="s">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+      <c r="H11" t="s">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12" t="s">
+        <v>50</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+      <c r="H12" t="s">
+        <v>10</v>
+      </c>
+      <c r="I12">
+        <v>1</v>
+      </c>
+      <c r="J12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>13</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+      <c r="H13" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14">
+        <v>12</v>
+      </c>
+      <c r="F14" t="s">
+        <v>36</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>16</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E15">
+        <v>12</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>9</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>17</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16" t="s">
+        <v>50</v>
+      </c>
+      <c r="E16">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>37</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="s">
+        <v>8</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>18</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17">
+        <v>13</v>
+      </c>
+      <c r="F17" t="s">
+        <v>37</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="s">
+        <v>9</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>19</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>14</v>
+      </c>
+      <c r="F18" t="s">
+        <v>38</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="s">
+        <v>11</v>
+      </c>
+      <c r="I18">
+        <v>1</v>
+      </c>
+      <c r="J18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19">
+        <v>1</v>
+      </c>
+      <c r="D19" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19">
+        <v>14</v>
+      </c>
+      <c r="F19" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="s">
+        <v>12</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>21</v>
+      </c>
+      <c r="B20">
+        <v>1</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20">
+        <v>15</v>
+      </c>
+      <c r="F20" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="s">
+        <v>8</v>
+      </c>
+      <c r="I20">
+        <v>1</v>
+      </c>
+      <c r="J20" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>22</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21">
+        <v>15</v>
+      </c>
+      <c r="F21" t="s">
+        <v>40</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="s">
+        <v>9</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A22">
+        <v>23</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22">
+        <v>1</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>16</v>
+      </c>
+      <c r="F22" t="s">
+        <v>41</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="s">
+        <v>8</v>
+      </c>
+      <c r="I22">
+        <v>1</v>
+      </c>
+      <c r="J22" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A23">
+        <v>24</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23">
+        <v>16</v>
+      </c>
+      <c r="F23" t="s">
+        <v>41</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>21</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A50D9B80-349C-450A-9037-EC263D91D03C}">
+  <dimension ref="A1:F10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="6" width="17.08984375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5">
+        <v>2</v>
+      </c>
+      <c r="E5" t="s">
+        <v>51</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>11</v>
+      </c>
+      <c r="B7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C7" t="s">
+        <v>67</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>12</v>
+      </c>
+      <c r="B8" t="s">
+        <v>68</v>
+      </c>
+      <c r="C8" t="s">
+        <v>69</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>13</v>
+      </c>
+      <c r="B9" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>17</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/Reference/Merge Table UI.xlsx
+++ b/Reference/Merge Table UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XenAnalyticTransl\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5A33E8F0-619E-490D-9DBE-9460DA7FCFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC14C926-6CAD-4138-9215-983B2ED69D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
   </bookViews>
@@ -414,8 +414,8 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4165,22 +4165,22 @@
       <c r="E4" t="s">
         <v>78</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G4" t="s">
-        <v>76</v>
-      </c>
-      <c r="H4" t="s">
+      <c r="G4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I4" t="s">
+      <c r="I4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K4" t="s">
+      <c r="K4" s="5" t="s">
         <v>4</v>
       </c>
     </row>
@@ -4200,22 +4200,22 @@
       <c r="E5" t="s">
         <v>78</v>
       </c>
-      <c r="F5" t="s">
+      <c r="F5" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G5" t="s">
-        <v>76</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="G5" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I5" t="s">
+      <c r="I5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K5" t="s">
+      <c r="K5" s="5" t="s">
         <v>5</v>
       </c>
     </row>
@@ -6925,23 +6925,23 @@
     <col min="1" max="6" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" s="4" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="4" t="s">
         <v>0</v>
       </c>
     </row>

--- a/Reference/Merge Table UI.xlsx
+++ b/Reference/Merge Table UI.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XenAnalyticTransl\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC14C926-6CAD-4138-9215-983B2ED69D45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1A040F-14FC-457C-86D5-05FE49ADCBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="2" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="hidden" r:id="rId1"/>
@@ -4515,22 +4515,22 @@
       <c r="E14" t="s">
         <v>87</v>
       </c>
-      <c r="F14" t="s">
+      <c r="F14" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G14" t="s">
-        <v>76</v>
-      </c>
-      <c r="H14" t="s">
+      <c r="G14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H14" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I14" t="s">
+      <c r="I14" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J14" t="s">
-        <v>76</v>
-      </c>
-      <c r="K14" t="s">
+      <c r="J14" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K14" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4550,22 +4550,22 @@
       <c r="E15" t="s">
         <v>87</v>
       </c>
-      <c r="F15" t="s">
+      <c r="F15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G15" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" t="s">
+      <c r="G15" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I15" t="s">
+      <c r="I15" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J15" t="s">
+      <c r="J15" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K15" t="s">
+      <c r="K15" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4585,22 +4585,22 @@
       <c r="E16" t="s">
         <v>88</v>
       </c>
-      <c r="F16" t="s">
+      <c r="F16" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H16" t="s">
+      <c r="G16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I16" t="s">
+      <c r="I16" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J16" t="s">
-        <v>76</v>
-      </c>
-      <c r="K16" t="s">
+      <c r="J16" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K16" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4620,22 +4620,22 @@
       <c r="E17" t="s">
         <v>88</v>
       </c>
-      <c r="F17" t="s">
+      <c r="F17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G17" t="s">
-        <v>76</v>
-      </c>
-      <c r="H17" t="s">
+      <c r="G17" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I17" t="s">
+      <c r="I17" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J17" t="s">
+      <c r="J17" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K17" t="s">
+      <c r="K17" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4725,22 +4725,22 @@
       <c r="E20" t="s">
         <v>89</v>
       </c>
-      <c r="F20" t="s">
+      <c r="F20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G20" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" t="s">
+      <c r="G20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I20" t="s">
+      <c r="I20" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J20" t="s">
-        <v>76</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="J20" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K20" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4760,22 +4760,22 @@
       <c r="E21" t="s">
         <v>89</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G21" t="s">
-        <v>76</v>
-      </c>
-      <c r="H21" t="s">
+      <c r="G21" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I21" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J21" t="s">
+      <c r="J21" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="5" t="s">
         <v>9</v>
       </c>
     </row>
@@ -4795,22 +4795,22 @@
       <c r="E22" t="s">
         <v>90</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G22" t="s">
-        <v>76</v>
-      </c>
-      <c r="H22" t="s">
+      <c r="G22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I22" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J22" t="s">
-        <v>76</v>
-      </c>
-      <c r="K22" t="s">
+      <c r="J22" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K22" s="5" t="s">
         <v>8</v>
       </c>
     </row>
@@ -4830,22 +4830,22 @@
       <c r="E23" t="s">
         <v>90</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="G23" t="s">
-        <v>76</v>
-      </c>
-      <c r="H23" t="s">
+      <c r="G23" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I23" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="J23" t="s">
+      <c r="J23" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="5" t="s">
         <v>9</v>
       </c>
     </row>

--- a/Reference/Merge Table UI.xlsx
+++ b/Reference/Merge Table UI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XenAnalyticTransl\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B1A040F-14FC-457C-86D5-05FE49ADCBE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E43D1D8-278F-484D-8A30-C809F0FDACAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" firstSheet="2" activeTab="6" xr2:uid="{31D85F91-40ED-4F68-9A5B-7EC9EBBDCEBE}"/>
   </bookViews>
@@ -6922,7 +6922,9 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="6" width="17.08984375" customWidth="1"/>
+    <col min="1" max="2" width="17.08984375" customWidth="1"/>
+    <col min="3" max="3" width="37.7265625" customWidth="1"/>
+    <col min="4" max="6" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.35">
